--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141DF1E7-9FEE-4D0B-AF59-846502460C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B940A3-F859-46D1-A934-02FA88CFF429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -705,9 +705,6 @@
     <t>mtdrumr</t>
   </si>
   <si>
-    <t>SebastiÃ¡n Solari</t>
-  </si>
-  <si>
     <t>TFabian</t>
   </si>
   <si>
@@ -841,6 +838,9 @@
   </si>
   <si>
     <t>Pendiente</t>
+  </si>
+  <si>
+    <t>Sebastian Solari</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1310,7 +1310,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -1380,7 +1380,7 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
@@ -1405,7 +1405,7 @@
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -1470,7 +1470,7 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
@@ -1485,7 +1485,7 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
@@ -1640,7 +1640,7 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
@@ -1685,12 +1685,12 @@
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
@@ -1750,12 +1750,12 @@
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
@@ -1770,12 +1770,12 @@
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
@@ -1850,7 +1850,7 @@
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
@@ -1880,17 +1880,17 @@
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
@@ -1940,7 +1940,7 @@
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
@@ -2030,17 +2030,17 @@
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
@@ -2060,17 +2060,17 @@
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
@@ -2105,7 +2105,7 @@
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
@@ -2115,7 +2115,7 @@
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
@@ -2190,7 +2190,7 @@
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
@@ -2225,7 +2225,7 @@
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
@@ -2390,7 +2390,7 @@
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
@@ -2400,12 +2400,12 @@
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
@@ -2500,12 +2500,12 @@
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">

--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A942BB-816D-41E0-A193-AD29A707649A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C74919-32B3-403B-A80A-147737B7C968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$A$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$A$266</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="284">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -826,9 +826,6 @@
   </si>
   <si>
     <t>Eduking</t>
-  </si>
-  <si>
-    <t>Nero2dd</t>
   </si>
   <si>
     <t>Pendiente</t>
@@ -1257,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1266,19 +1263,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" t="s">
         <v>266</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>267</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" t="s">
         <v>268</v>
-      </c>
-      <c r="D1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1286,7 +1283,7 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D2">
         <v>51</v>
@@ -1301,7 +1298,7 @@
         <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D3">
         <v>51</v>
@@ -1316,7 +1313,7 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D4">
         <v>51</v>
@@ -1331,7 +1328,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -1342,9 +1339,15 @@
       <c r="A6" t="s">
         <v>83</v>
       </c>
+      <c r="C6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6">
+        <v>51</v>
+      </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1361,7 +1364,7 @@
         <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -1373,7 +1376,7 @@
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -1388,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D10">
         <v>51</v>
@@ -1403,7 +1406,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D11">
         <v>52</v>
@@ -1418,7 +1421,7 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D12">
         <v>52</v>
@@ -1433,7 +1436,7 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D13">
         <v>51</v>
@@ -1448,7 +1451,7 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D14">
         <v>51</v>
@@ -1463,7 +1466,7 @@
         <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D15">
         <v>51</v>
@@ -1478,7 +1481,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D16">
         <v>51</v>
@@ -1502,7 +1505,7 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D18">
         <v>51</v>
@@ -1517,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D19">
         <v>51</v>
@@ -1532,7 +1535,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -1628,7 +1631,7 @@
         <v>933448842</v>
       </c>
       <c r="C30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D30">
         <v>51</v>
@@ -1643,7 +1646,7 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -1676,10 +1679,10 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D34">
         <v>54</v>
@@ -1711,9 +1714,15 @@
       <c r="A37" t="s">
         <v>258</v>
       </c>
+      <c r="C37" t="s">
+        <v>275</v>
+      </c>
+      <c r="D37">
+        <v>51</v>
+      </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1730,7 +1739,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D39">
         <v>51</v>
@@ -1745,7 +1754,7 @@
         <v>185</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D40">
         <v>51</v>
@@ -1768,18 +1777,30 @@
       <c r="A42" t="s">
         <v>223</v>
       </c>
+      <c r="C42" t="s">
+        <v>275</v>
+      </c>
+      <c r="D42">
+        <v>51</v>
+      </c>
       <c r="E42" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
+      <c r="C43" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43">
+        <v>51</v>
+      </c>
       <c r="E43" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1787,7 +1808,7 @@
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D44">
         <v>51</v>
@@ -1838,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D49">
         <v>51</v>
@@ -1889,7 +1910,7 @@
         <v>161</v>
       </c>
       <c r="C54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D54">
         <v>51</v>
@@ -1913,7 +1934,7 @@
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D56">
         <v>51</v>
@@ -1991,10 +2012,10 @@
         <v>39</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2062,9 +2083,15 @@
       <c r="A71" t="s">
         <v>74</v>
       </c>
+      <c r="C71" t="s">
+        <v>275</v>
+      </c>
+      <c r="D71">
+        <v>51</v>
+      </c>
       <c r="E71" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2116,18 +2143,30 @@
       <c r="A77" t="s">
         <v>31</v>
       </c>
+      <c r="C77" t="s">
+        <v>275</v>
+      </c>
+      <c r="D77">
+        <v>51</v>
+      </c>
       <c r="E77" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>88</v>
       </c>
+      <c r="C78" t="s">
+        <v>275</v>
+      </c>
+      <c r="D78">
+        <v>51</v>
+      </c>
       <c r="E78" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2188,9 +2227,15 @@
       <c r="A85" t="s">
         <v>44</v>
       </c>
+      <c r="C85" t="s">
+        <v>275</v>
+      </c>
+      <c r="D85">
+        <v>51</v>
+      </c>
       <c r="E85" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2206,9 +2251,15 @@
       <c r="A87" t="s">
         <v>162</v>
       </c>
+      <c r="C87" t="s">
+        <v>275</v>
+      </c>
+      <c r="D87">
+        <v>51</v>
+      </c>
       <c r="E87" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2306,10 +2357,10 @@
         <v>241</v>
       </c>
       <c r="B98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C98" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D98">
         <v>54</v>
@@ -2333,10 +2384,10 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C100" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D100">
         <v>53</v>
@@ -2395,9 +2446,15 @@
       <c r="A106" t="s">
         <v>169</v>
       </c>
+      <c r="C106" t="s">
+        <v>275</v>
+      </c>
+      <c r="D106">
+        <v>51</v>
+      </c>
       <c r="E106" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2575,18 +2632,30 @@
       <c r="A126" t="s">
         <v>21</v>
       </c>
+      <c r="C126" t="s">
+        <v>275</v>
+      </c>
+      <c r="D126">
+        <v>51</v>
+      </c>
       <c r="E126" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>77</v>
       </c>
+      <c r="C127" t="s">
+        <v>275</v>
+      </c>
+      <c r="D127">
+        <v>51</v>
+      </c>
       <c r="E127" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -2675,10 +2744,10 @@
         <v>261</v>
       </c>
       <c r="B137" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C137" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D137">
         <v>54</v>
@@ -2701,9 +2770,15 @@
       <c r="A139" t="s">
         <v>33</v>
       </c>
+      <c r="C139" t="s">
+        <v>272</v>
+      </c>
+      <c r="D139">
+        <v>52</v>
+      </c>
       <c r="E139" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+52 </v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -2773,9 +2848,15 @@
       <c r="A147" t="s">
         <v>25</v>
       </c>
+      <c r="C147" t="s">
+        <v>275</v>
+      </c>
+      <c r="D147">
+        <v>51</v>
+      </c>
       <c r="E147" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -2845,9 +2926,15 @@
       <c r="A155" t="s">
         <v>118</v>
       </c>
+      <c r="C155" t="s">
+        <v>275</v>
+      </c>
+      <c r="D155">
+        <v>51</v>
+      </c>
       <c r="E155" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -2855,10 +2942,10 @@
         <v>173</v>
       </c>
       <c r="B156" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C156" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D156">
         <v>52</v>
@@ -2890,9 +2977,15 @@
       <c r="A159" t="s">
         <v>93</v>
       </c>
+      <c r="C159" t="s">
+        <v>275</v>
+      </c>
+      <c r="D159">
+        <v>51</v>
+      </c>
       <c r="E159" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -2908,9 +3001,15 @@
       <c r="A161" t="s">
         <v>72</v>
       </c>
+      <c r="C161" t="s">
+        <v>275</v>
+      </c>
+      <c r="D161">
+        <v>51</v>
+      </c>
       <c r="E161" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -2926,18 +3025,30 @@
       <c r="A163" t="s">
         <v>87</v>
       </c>
+      <c r="C163" t="s">
+        <v>275</v>
+      </c>
+      <c r="D163">
+        <v>51</v>
+      </c>
       <c r="E163" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>75</v>
       </c>
+      <c r="C164" t="s">
+        <v>275</v>
+      </c>
+      <c r="D164">
+        <v>51</v>
+      </c>
       <c r="E164" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -2945,7 +3056,7 @@
         <v>202</v>
       </c>
       <c r="E165" t="str">
-        <f t="shared" ref="E165:E228" si="3">CONCATENATE("+",D165," ",B165)</f>
+        <f t="shared" ref="E165:E227" si="3">CONCATENATE("+",D165," ",B165)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
@@ -2971,18 +3082,30 @@
       <c r="A168" t="s">
         <v>248</v>
       </c>
+      <c r="C168" t="s">
+        <v>275</v>
+      </c>
+      <c r="D168">
+        <v>51</v>
+      </c>
       <c r="E168" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>78</v>
       </c>
+      <c r="C169" t="s">
+        <v>275</v>
+      </c>
+      <c r="D169">
+        <v>51</v>
+      </c>
       <c r="E169" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -3070,9 +3193,15 @@
       <c r="A179" t="s">
         <v>219</v>
       </c>
+      <c r="C179" t="s">
+        <v>275</v>
+      </c>
+      <c r="D179">
+        <v>51</v>
+      </c>
       <c r="E179" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -3089,10 +3218,10 @@
         <v>260</v>
       </c>
       <c r="B181" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C181" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D181">
         <v>53</v>
@@ -3113,7 +3242,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>263</v>
+        <v>132</v>
       </c>
       <c r="E183" t="str">
         <f t="shared" si="3"/>
@@ -3122,16 +3251,22 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>132</v>
+        <v>29</v>
+      </c>
+      <c r="C184" t="s">
+        <v>275</v>
+      </c>
+      <c r="D184">
+        <v>51</v>
       </c>
       <c r="E184" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E185" t="str">
         <f t="shared" si="3"/>
@@ -3140,7 +3275,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E186" t="str">
         <f t="shared" si="3"/>
@@ -3149,7 +3284,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E187" t="str">
         <f t="shared" si="3"/>
@@ -3158,7 +3293,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E188" t="str">
         <f t="shared" si="3"/>
@@ -3167,7 +3302,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="E189" t="str">
         <f t="shared" si="3"/>
@@ -3176,7 +3311,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="E190" t="str">
         <f t="shared" si="3"/>
@@ -3185,7 +3320,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E191" t="str">
         <f t="shared" si="3"/>
@@ -3194,16 +3329,22 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>208</v>
+        <v>3</v>
+      </c>
+      <c r="C192" t="s">
+        <v>275</v>
+      </c>
+      <c r="D192">
+        <v>51</v>
       </c>
       <c r="E192" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="E193" t="str">
         <f t="shared" si="3"/>
@@ -3212,7 +3353,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="E194" t="str">
         <f t="shared" si="3"/>
@@ -3221,7 +3362,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="E195" t="str">
         <f t="shared" si="3"/>
@@ -3230,16 +3371,22 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>152</v>
+        <v>103</v>
+      </c>
+      <c r="C196" t="s">
+        <v>275</v>
+      </c>
+      <c r="D196">
+        <v>51</v>
       </c>
       <c r="E196" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>103</v>
+        <v>263</v>
       </c>
       <c r="E197" t="str">
         <f t="shared" si="3"/>
@@ -3248,7 +3395,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="E198" t="str">
         <f t="shared" si="3"/>
@@ -3257,7 +3404,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="E199" t="str">
         <f t="shared" si="3"/>
@@ -3266,7 +3413,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="E200" t="str">
         <f t="shared" si="3"/>
@@ -3275,16 +3422,22 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>205</v>
+        <v>174</v>
+      </c>
+      <c r="C201" t="s">
+        <v>275</v>
+      </c>
+      <c r="D201">
+        <v>51</v>
       </c>
       <c r="E201" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="E202" t="str">
         <f t="shared" si="3"/>
@@ -3293,7 +3446,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="E203" t="str">
         <f t="shared" si="3"/>
@@ -3302,7 +3455,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>48</v>
+        <v>252</v>
       </c>
       <c r="E204" t="str">
         <f t="shared" si="3"/>
@@ -3311,7 +3464,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
       <c r="E205" t="str">
         <f t="shared" si="3"/>
@@ -3320,7 +3473,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="E206" t="str">
         <f t="shared" si="3"/>
@@ -3329,16 +3482,22 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>151</v>
+        <v>183</v>
+      </c>
+      <c r="C207" t="s">
+        <v>275</v>
+      </c>
+      <c r="D207">
+        <v>51</v>
       </c>
       <c r="E207" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E208" t="str">
         <f t="shared" si="3"/>
@@ -3347,7 +3506,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>197</v>
+        <v>96</v>
       </c>
       <c r="E209" t="str">
         <f t="shared" si="3"/>
@@ -3356,7 +3515,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>96</v>
+        <v>254</v>
       </c>
       <c r="E210" t="str">
         <f t="shared" si="3"/>
@@ -3365,25 +3524,37 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>254</v>
+        <v>97</v>
+      </c>
+      <c r="C211" t="s">
+        <v>275</v>
+      </c>
+      <c r="D211">
+        <v>51</v>
       </c>
       <c r="E211" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>97</v>
+        <v>28</v>
+      </c>
+      <c r="C212" t="s">
+        <v>275</v>
+      </c>
+      <c r="D212">
+        <v>51</v>
       </c>
       <c r="E212" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="E213" t="str">
         <f t="shared" si="3"/>
@@ -3392,7 +3563,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="E214" t="str">
         <f t="shared" si="3"/>
@@ -3401,25 +3572,37 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>145</v>
+        <v>7</v>
+      </c>
+      <c r="C215" t="s">
+        <v>275</v>
+      </c>
+      <c r="D215">
+        <v>51</v>
       </c>
       <c r="E215" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C216" t="s">
+        <v>275</v>
+      </c>
+      <c r="D216">
+        <v>51</v>
       </c>
       <c r="E216" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>15</v>
+        <v>239</v>
       </c>
       <c r="E217" t="str">
         <f t="shared" si="3"/>
@@ -3428,7 +3611,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="E218" t="str">
         <f t="shared" si="3"/>
@@ -3437,7 +3620,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="E219" t="str">
         <f t="shared" si="3"/>
@@ -3446,7 +3629,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="E220" t="str">
         <f t="shared" si="3"/>
@@ -3455,7 +3638,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E221" t="str">
         <f t="shared" si="3"/>
@@ -3464,7 +3647,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E222" t="str">
         <f t="shared" si="3"/>
@@ -3473,7 +3656,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="E223" t="str">
         <f t="shared" si="3"/>
@@ -3482,7 +3665,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="E224" t="str">
         <f t="shared" si="3"/>
@@ -3491,7 +3674,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E225" t="str">
         <f t="shared" si="3"/>
@@ -3500,7 +3683,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="E226" t="str">
         <f t="shared" si="3"/>
@@ -3509,7 +3692,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="E227" t="str">
         <f t="shared" si="3"/>
@@ -3518,25 +3701,25 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="E228" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E228:E266" si="4">CONCATENATE("+",D228," ",B228)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E229" t="str">
-        <f t="shared" ref="E229:E267" si="4">CONCATENATE("+",D229," ",B229)</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="E230" t="str">
         <f t="shared" si="4"/>
@@ -3545,7 +3728,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="E231" t="str">
         <f t="shared" si="4"/>
@@ -3554,7 +3737,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="E232" t="str">
         <f t="shared" si="4"/>
@@ -3563,7 +3746,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E233" t="str">
         <f t="shared" si="4"/>
@@ -3572,7 +3755,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="E234" t="str">
         <f t="shared" si="4"/>
@@ -3581,25 +3764,37 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>123</v>
+        <v>73</v>
+      </c>
+      <c r="C235" t="s">
+        <v>275</v>
+      </c>
+      <c r="D235">
+        <v>51</v>
       </c>
       <c r="E235" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>73</v>
+        <v>85</v>
+      </c>
+      <c r="C236" t="s">
+        <v>275</v>
+      </c>
+      <c r="D236">
+        <v>51</v>
       </c>
       <c r="E236" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>85</v>
+        <v>227</v>
       </c>
       <c r="E237" t="str">
         <f t="shared" si="4"/>
@@ -3608,7 +3803,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>227</v>
+        <v>143</v>
       </c>
       <c r="E238" t="str">
         <f t="shared" si="4"/>
@@ -3617,7 +3812,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>143</v>
+        <v>221</v>
       </c>
       <c r="E239" t="str">
         <f t="shared" si="4"/>
@@ -3626,61 +3821,79 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>221</v>
+        <v>259</v>
+      </c>
+      <c r="C240" t="s">
+        <v>275</v>
+      </c>
+      <c r="D240">
+        <v>51</v>
       </c>
       <c r="E240" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>259</v>
+        <v>81</v>
+      </c>
+      <c r="C241" t="s">
+        <v>275</v>
+      </c>
+      <c r="D241">
+        <v>51</v>
       </c>
       <c r="E241" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>81</v>
+        <v>19</v>
+      </c>
+      <c r="C242" t="s">
+        <v>275</v>
+      </c>
+      <c r="D242">
+        <v>51</v>
       </c>
       <c r="E242" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="B243">
+        <v>972691544</v>
+      </c>
+      <c r="C243" t="s">
+        <v>275</v>
+      </c>
+      <c r="D243">
+        <v>51</v>
       </c>
       <c r="E243" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 972691544</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>13</v>
-      </c>
-      <c r="B244">
-        <v>972691544</v>
-      </c>
-      <c r="C244" t="s">
-        <v>276</v>
-      </c>
-      <c r="D244">
-        <v>51</v>
+        <v>187</v>
       </c>
       <c r="E244" t="str">
         <f t="shared" si="4"/>
-        <v>+51 972691544</v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="E245" t="str">
         <f t="shared" si="4"/>
@@ -3689,7 +3902,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E246" t="str">
         <f t="shared" si="4"/>
@@ -3698,16 +3911,22 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>214</v>
+        <v>131</v>
+      </c>
+      <c r="C247" t="s">
+        <v>275</v>
+      </c>
+      <c r="D247">
+        <v>51</v>
       </c>
       <c r="E247" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>131</v>
+        <v>233</v>
       </c>
       <c r="E248" t="str">
         <f t="shared" si="4"/>
@@ -3716,25 +3935,37 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>233</v>
+        <v>76</v>
+      </c>
+      <c r="C249" t="s">
+        <v>275</v>
+      </c>
+      <c r="D249">
+        <v>51</v>
       </c>
       <c r="E249" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="C250" t="s">
+        <v>275</v>
+      </c>
+      <c r="D250">
+        <v>51</v>
       </c>
       <c r="E250" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E251" t="str">
         <f t="shared" si="4"/>
@@ -3743,25 +3974,37 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>24</v>
+        <v>102</v>
+      </c>
+      <c r="C252" t="s">
+        <v>275</v>
+      </c>
+      <c r="D252">
+        <v>51</v>
       </c>
       <c r="E252" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>102</v>
+        <v>171</v>
+      </c>
+      <c r="C253" t="s">
+        <v>275</v>
+      </c>
+      <c r="D253">
+        <v>51</v>
       </c>
       <c r="E253" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E254" t="str">
         <f t="shared" si="4"/>
@@ -3770,7 +4013,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="E255" t="str">
         <f t="shared" si="4"/>
@@ -3779,7 +4022,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="E256" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +4031,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="E257" t="str">
         <f t="shared" si="4"/>
@@ -3797,7 +4040,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>210</v>
+        <v>63</v>
       </c>
       <c r="E258" t="str">
         <f t="shared" si="4"/>
@@ -3806,7 +4049,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="E259" t="str">
         <f t="shared" si="4"/>
@@ -3815,7 +4058,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E260" t="str">
         <f t="shared" si="4"/>
@@ -3824,7 +4067,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="E261" t="str">
         <f t="shared" si="4"/>
@@ -3833,7 +4076,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="E262" t="str">
         <f t="shared" si="4"/>
@@ -3842,7 +4085,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="E263" t="str">
         <f t="shared" si="4"/>
@@ -3851,7 +4094,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="E264" t="str">
         <f t="shared" si="4"/>
@@ -3860,7 +4103,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="E265" t="str">
         <f t="shared" si="4"/>
@@ -3869,40 +4112,31 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E266" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>11</v>
-      </c>
-      <c r="E267" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
+    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
-      <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
-    </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B278" s="2"/>
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
+      <c r="B277" s="2"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
+      <c r="E277" s="2"/>
+      <c r="F277" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A267" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A267">
-    <sortCondition ref="A2:A267"/>
+  <autoFilter ref="A1:A266" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A266">
+    <sortCondition ref="A2:A266"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C74919-32B3-403B-A80A-147737B7C968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33031367-9B3B-425A-AB6E-4E0019D147F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$A$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$A$265</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="283">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -619,9 +619,6 @@
   </si>
   <si>
     <t>Jonus</t>
-  </si>
-  <si>
-    <t>JadenKnight</t>
   </si>
   <si>
     <t>afroier</t>
@@ -1254,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1263,19 +1260,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" t="s">
         <v>265</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>266</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" t="s">
         <v>267</v>
-      </c>
-      <c r="D1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1283,7 +1280,7 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D2">
         <v>51</v>
@@ -1295,10 +1292,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D3">
         <v>51</v>
@@ -1313,7 +1310,7 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4">
         <v>51</v>
@@ -1328,7 +1325,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -1340,7 +1337,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6">
         <v>51</v>
@@ -1352,7 +1349,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -1361,10 +1358,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -1376,7 +1373,7 @@
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -1391,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D10">
         <v>51</v>
@@ -1406,7 +1403,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D11">
         <v>52</v>
@@ -1421,7 +1418,7 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D12">
         <v>52</v>
@@ -1436,7 +1433,7 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D13">
         <v>51</v>
@@ -1451,7 +1448,7 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D14">
         <v>51</v>
@@ -1466,7 +1463,7 @@
         <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D15">
         <v>51</v>
@@ -1481,7 +1478,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D16">
         <v>51</v>
@@ -1505,7 +1502,7 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D18">
         <v>51</v>
@@ -1520,7 +1517,7 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D19">
         <v>51</v>
@@ -1535,7 +1532,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -1562,7 +1559,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -1616,7 +1613,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -1631,7 +1628,7 @@
         <v>933448842</v>
       </c>
       <c r="C30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D30">
         <v>51</v>
@@ -1646,7 +1643,7 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -1679,10 +1676,10 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D34">
         <v>54</v>
@@ -1712,10 +1709,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D37">
         <v>51</v>
@@ -1739,7 +1736,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D39">
         <v>51</v>
@@ -1754,7 +1751,7 @@
         <v>185</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D40">
         <v>51</v>
@@ -1775,10 +1772,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D42">
         <v>51</v>
@@ -1793,7 +1790,7 @@
         <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -1808,7 +1805,7 @@
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D44">
         <v>51</v>
@@ -1820,7 +1817,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E45" t="str">
         <f t="shared" si="0"/>
@@ -1859,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D49">
         <v>51</v>
@@ -1910,7 +1907,7 @@
         <v>161</v>
       </c>
       <c r="C54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D54">
         <v>51</v>
@@ -1934,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D56">
         <v>51</v>
@@ -1946,7 +1943,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E57" t="str">
         <f t="shared" si="0"/>
@@ -2000,7 +1997,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E63" t="str">
         <f t="shared" si="0"/>
@@ -2012,10 +2009,10 @@
         <v>39</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2054,7 +2051,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E68" t="str">
         <f t="shared" si="1"/>
@@ -2084,7 +2081,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D71">
         <v>51</v>
@@ -2096,7 +2093,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" si="1"/>
@@ -2105,7 +2102,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="1"/>
@@ -2132,7 +2129,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="1"/>
@@ -2144,7 +2141,7 @@
         <v>31</v>
       </c>
       <c r="C77" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D77">
         <v>51</v>
@@ -2159,7 +2156,7 @@
         <v>88</v>
       </c>
       <c r="C78" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D78">
         <v>51</v>
@@ -2198,7 +2195,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E82" t="str">
         <f t="shared" si="1"/>
@@ -2228,7 +2225,7 @@
         <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D85">
         <v>51</v>
@@ -2252,7 +2249,7 @@
         <v>162</v>
       </c>
       <c r="C87" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D87">
         <v>51</v>
@@ -2264,7 +2261,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E88" t="str">
         <f t="shared" si="1"/>
@@ -2300,7 +2297,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E92" t="str">
         <f t="shared" si="1"/>
@@ -2336,7 +2333,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="1"/>
@@ -2345,7 +2342,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" si="1"/>
@@ -2354,13 +2351,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B98" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C98" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D98">
         <v>54</v>
@@ -2384,10 +2381,10 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D100">
         <v>53</v>
@@ -2402,13 +2399,13 @@
         <v>140</v>
       </c>
       <c r="E101" t="str">
-        <f t="shared" ref="E101:E164" si="2">CONCATENATE("+",D101," ",B101)</f>
+        <f t="shared" ref="E101:E163" si="2">CONCATENATE("+",D101," ",B101)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E102" t="str">
         <f t="shared" si="2"/>
@@ -2447,7 +2444,7 @@
         <v>169</v>
       </c>
       <c r="C106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D106">
         <v>51</v>
@@ -2459,7 +2456,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E107" t="str">
         <f t="shared" si="2"/>
@@ -2486,7 +2483,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E110" t="str">
         <f t="shared" si="2"/>
@@ -2495,7 +2492,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E111" t="str">
         <f t="shared" si="2"/>
@@ -2522,7 +2519,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E114" t="str">
         <f t="shared" si="2"/>
@@ -2531,7 +2528,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E115" t="str">
         <f t="shared" si="2"/>
@@ -2567,7 +2564,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="E119" t="str">
         <f t="shared" si="2"/>
@@ -2576,7 +2573,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E120" t="str">
         <f t="shared" si="2"/>
@@ -2585,7 +2582,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="E121" t="str">
         <f t="shared" si="2"/>
@@ -2594,7 +2591,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="E122" t="str">
         <f t="shared" si="2"/>
@@ -2603,7 +2600,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="E123" t="str">
         <f t="shared" si="2"/>
@@ -2612,7 +2609,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>211</v>
+        <v>2</v>
       </c>
       <c r="E124" t="str">
         <f t="shared" si="2"/>
@@ -2621,19 +2618,25 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="C125" t="s">
+        <v>274</v>
+      </c>
+      <c r="D125">
+        <v>51</v>
       </c>
       <c r="E125" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C126" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D126">
         <v>51</v>
@@ -2645,22 +2648,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>77</v>
-      </c>
-      <c r="C127" t="s">
-        <v>275</v>
-      </c>
-      <c r="D127">
-        <v>51</v>
+        <v>252</v>
       </c>
       <c r="E127" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="E128" t="str">
         <f t="shared" si="2"/>
@@ -2669,7 +2666,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="E129" t="str">
         <f t="shared" si="2"/>
@@ -2678,7 +2675,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="E130" t="str">
         <f t="shared" si="2"/>
@@ -2687,7 +2684,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="E131" t="str">
         <f t="shared" si="2"/>
@@ -2696,7 +2693,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="E132" t="str">
         <f t="shared" si="2"/>
@@ -2705,7 +2702,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="E133" t="str">
         <f t="shared" si="2"/>
@@ -2714,7 +2711,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="E134" t="str">
         <f t="shared" si="2"/>
@@ -2723,7 +2720,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>47</v>
+        <v>221</v>
       </c>
       <c r="E135" t="str">
         <f t="shared" si="2"/>
@@ -2732,58 +2729,58 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>222</v>
+        <v>260</v>
+      </c>
+      <c r="B136" t="s">
+        <v>279</v>
+      </c>
+      <c r="C136" t="s">
+        <v>276</v>
+      </c>
+      <c r="D136">
+        <v>54</v>
       </c>
       <c r="E136" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+54 9 11 2526 8333</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>261</v>
-      </c>
-      <c r="B137" t="s">
-        <v>280</v>
-      </c>
-      <c r="C137" t="s">
-        <v>277</v>
-      </c>
-      <c r="D137">
-        <v>54</v>
+        <v>250</v>
       </c>
       <c r="E137" t="str">
         <f t="shared" si="2"/>
-        <v>+54 9 11 2526 8333</v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>251</v>
+        <v>33</v>
+      </c>
+      <c r="C138" t="s">
+        <v>271</v>
+      </c>
+      <c r="D138">
+        <v>52</v>
       </c>
       <c r="E138" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+52 </v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>33</v>
-      </c>
-      <c r="C139" t="s">
-        <v>272</v>
-      </c>
-      <c r="D139">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="E139" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+52 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="E140" t="str">
         <f t="shared" si="2"/>
@@ -2792,7 +2789,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="E141" t="str">
         <f t="shared" si="2"/>
@@ -2801,7 +2798,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="E142" t="str">
         <f t="shared" si="2"/>
@@ -2810,7 +2807,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="E143" t="str">
         <f t="shared" si="2"/>
@@ -2819,7 +2816,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E144" t="str">
         <f t="shared" si="2"/>
@@ -2828,7 +2825,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="E145" t="str">
         <f t="shared" si="2"/>
@@ -2837,31 +2834,31 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>213</v>
+        <v>25</v>
+      </c>
+      <c r="C146" t="s">
+        <v>274</v>
+      </c>
+      <c r="D146">
+        <v>51</v>
       </c>
       <c r="E146" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" t="s">
-        <v>275</v>
-      </c>
-      <c r="D147">
-        <v>51</v>
+        <v>246</v>
       </c>
       <c r="E147" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="E148" t="str">
         <f t="shared" si="2"/>
@@ -2870,7 +2867,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E149" t="str">
         <f t="shared" si="2"/>
@@ -2879,7 +2876,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="E150" t="str">
         <f t="shared" si="2"/>
@@ -2888,7 +2885,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E151" t="str">
         <f t="shared" si="2"/>
@@ -2897,7 +2894,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>186</v>
+        <v>65</v>
       </c>
       <c r="E152" t="str">
         <f t="shared" si="2"/>
@@ -2906,7 +2903,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="E153" t="str">
         <f t="shared" si="2"/>
@@ -2915,49 +2912,49 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>4</v>
+        <v>118</v>
+      </c>
+      <c r="C154" t="s">
+        <v>274</v>
+      </c>
+      <c r="D154">
+        <v>51</v>
       </c>
       <c r="E154" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>118</v>
+        <v>173</v>
+      </c>
+      <c r="B155" t="s">
+        <v>272</v>
       </c>
       <c r="C155" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D155">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E155" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+52 1 771 297 6010</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>173</v>
-      </c>
-      <c r="B156" t="s">
-        <v>273</v>
-      </c>
-      <c r="C156" t="s">
-        <v>272</v>
-      </c>
-      <c r="D156">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="E156" t="str">
         <f t="shared" si="2"/>
-        <v>+52 1 771 297 6010</v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="E157" t="str">
         <f t="shared" si="2"/>
@@ -2966,67 +2963,73 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>189</v>
+        <v>93</v>
+      </c>
+      <c r="C158" t="s">
+        <v>274</v>
+      </c>
+      <c r="D158">
+        <v>51</v>
       </c>
       <c r="E158" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>93</v>
-      </c>
-      <c r="C159" t="s">
-        <v>275</v>
-      </c>
-      <c r="D159">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="E159" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>153</v>
+        <v>72</v>
+      </c>
+      <c r="C160" t="s">
+        <v>274</v>
+      </c>
+      <c r="D160">
+        <v>51</v>
       </c>
       <c r="E160" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>72</v>
-      </c>
-      <c r="C161" t="s">
-        <v>275</v>
-      </c>
-      <c r="D161">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E161" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="C162" t="s">
+        <v>274</v>
+      </c>
+      <c r="D162">
+        <v>51</v>
       </c>
       <c r="E162" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C163" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D163">
         <v>51</v>
@@ -3038,31 +3041,25 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>75</v>
-      </c>
-      <c r="C164" t="s">
-        <v>275</v>
-      </c>
-      <c r="D164">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="E164" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" ref="E164:E226" si="3">CONCATENATE("+",D164," ",B164)</f>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="E165" t="str">
-        <f t="shared" ref="E165:E227" si="3">CONCATENATE("+",D165," ",B165)</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E166" t="str">
         <f t="shared" si="3"/>
@@ -3071,19 +3068,25 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>255</v>
+        <v>247</v>
+      </c>
+      <c r="C167" t="s">
+        <v>274</v>
+      </c>
+      <c r="D167">
+        <v>51</v>
       </c>
       <c r="E167" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="C168" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D168">
         <v>51</v>
@@ -3095,22 +3098,16 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>78</v>
-      </c>
-      <c r="C169" t="s">
-        <v>275</v>
-      </c>
-      <c r="D169">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="E169" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="E170" t="str">
         <f t="shared" si="3"/>
@@ -3119,7 +3116,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
       <c r="E171" t="str">
         <f t="shared" si="3"/>
@@ -3128,7 +3125,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E172" t="str">
         <f t="shared" si="3"/>
@@ -3137,7 +3134,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E173" t="str">
         <f t="shared" si="3"/>
@@ -3146,7 +3143,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>246</v>
+        <v>35</v>
       </c>
       <c r="E174" t="str">
         <f t="shared" si="3"/>
@@ -3155,7 +3152,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
       <c r="E175" t="str">
         <f t="shared" si="3"/>
@@ -3164,7 +3161,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E176" t="str">
         <f t="shared" si="3"/>
@@ -3173,7 +3170,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="E177" t="str">
         <f t="shared" si="3"/>
@@ -3182,58 +3179,58 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>69</v>
+        <v>218</v>
+      </c>
+      <c r="C178" t="s">
+        <v>274</v>
+      </c>
+      <c r="D178">
+        <v>51</v>
       </c>
       <c r="E178" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>219</v>
-      </c>
-      <c r="C179" t="s">
-        <v>275</v>
-      </c>
-      <c r="D179">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="E179" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>167</v>
+        <v>259</v>
+      </c>
+      <c r="B180" t="s">
+        <v>280</v>
+      </c>
+      <c r="C180" t="s">
+        <v>269</v>
+      </c>
+      <c r="D180">
+        <v>53</v>
       </c>
       <c r="E180" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+53 5 6957902</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>260</v>
-      </c>
-      <c r="B181" t="s">
-        <v>281</v>
-      </c>
-      <c r="C181" t="s">
-        <v>270</v>
-      </c>
-      <c r="D181">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="E181" t="str">
         <f t="shared" si="3"/>
-        <v>+53 5 6957902</v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E182" t="str">
         <f t="shared" si="3"/>
@@ -3242,31 +3239,31 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>132</v>
+        <v>29</v>
+      </c>
+      <c r="C183" t="s">
+        <v>274</v>
+      </c>
+      <c r="D183">
+        <v>51</v>
       </c>
       <c r="E183" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>29</v>
-      </c>
-      <c r="C184" t="s">
-        <v>275</v>
-      </c>
-      <c r="D184">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E184" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E185" t="str">
         <f t="shared" si="3"/>
@@ -3275,7 +3272,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E186" t="str">
         <f t="shared" si="3"/>
@@ -3284,7 +3281,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E187" t="str">
         <f t="shared" si="3"/>
@@ -3293,7 +3290,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="E188" t="str">
         <f t="shared" si="3"/>
@@ -3302,7 +3299,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="E189" t="str">
         <f t="shared" si="3"/>
@@ -3311,7 +3308,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E190" t="str">
         <f t="shared" si="3"/>
@@ -3320,31 +3317,31 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>208</v>
+        <v>3</v>
+      </c>
+      <c r="C191" t="s">
+        <v>274</v>
+      </c>
+      <c r="D191">
+        <v>51</v>
       </c>
       <c r="E191" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" t="s">
-        <v>275</v>
-      </c>
-      <c r="D192">
-        <v>51</v>
+        <v>172</v>
       </c>
       <c r="E192" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="E193" t="str">
         <f t="shared" si="3"/>
@@ -3353,7 +3350,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="E194" t="str">
         <f t="shared" si="3"/>
@@ -3362,31 +3359,31 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>152</v>
+        <v>103</v>
+      </c>
+      <c r="C195" t="s">
+        <v>274</v>
+      </c>
+      <c r="D195">
+        <v>51</v>
       </c>
       <c r="E195" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>103</v>
-      </c>
-      <c r="C196" t="s">
-        <v>275</v>
-      </c>
-      <c r="D196">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="E196" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="E197" t="str">
         <f t="shared" si="3"/>
@@ -3395,7 +3392,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="E198" t="str">
         <f t="shared" si="3"/>
@@ -3404,7 +3401,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E199" t="str">
         <f t="shared" si="3"/>
@@ -3413,31 +3410,31 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>205</v>
+        <v>174</v>
+      </c>
+      <c r="C200" t="s">
+        <v>274</v>
+      </c>
+      <c r="D200">
+        <v>51</v>
       </c>
       <c r="E200" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>174</v>
-      </c>
-      <c r="C201" t="s">
-        <v>275</v>
-      </c>
-      <c r="D201">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="E201" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="E202" t="str">
         <f t="shared" si="3"/>
@@ -3446,7 +3443,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>48</v>
+        <v>251</v>
       </c>
       <c r="E203" t="str">
         <f t="shared" si="3"/>
@@ -3455,7 +3452,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="E204" t="str">
         <f t="shared" si="3"/>
@@ -3464,7 +3461,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="E205" t="str">
         <f t="shared" si="3"/>
@@ -3473,31 +3470,31 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>151</v>
+        <v>183</v>
+      </c>
+      <c r="C206" t="s">
+        <v>274</v>
+      </c>
+      <c r="D206">
+        <v>51</v>
       </c>
       <c r="E206" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>183</v>
-      </c>
-      <c r="C207" t="s">
-        <v>275</v>
-      </c>
-      <c r="D207">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="E207" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>197</v>
+        <v>96</v>
       </c>
       <c r="E208" t="str">
         <f t="shared" si="3"/>
@@ -3506,7 +3503,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>96</v>
+        <v>253</v>
       </c>
       <c r="E209" t="str">
         <f t="shared" si="3"/>
@@ -3515,19 +3512,25 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>254</v>
+        <v>97</v>
+      </c>
+      <c r="C210" t="s">
+        <v>274</v>
+      </c>
+      <c r="D210">
+        <v>51</v>
       </c>
       <c r="E210" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C211" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D211">
         <v>51</v>
@@ -3539,22 +3542,16 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>28</v>
-      </c>
-      <c r="C212" t="s">
-        <v>275</v>
-      </c>
-      <c r="D212">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="E212" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="E213" t="str">
         <f t="shared" si="3"/>
@@ -3563,19 +3560,25 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>145</v>
+        <v>7</v>
+      </c>
+      <c r="C214" t="s">
+        <v>274</v>
+      </c>
+      <c r="D214">
+        <v>51</v>
       </c>
       <c r="E214" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C215" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D215">
         <v>51</v>
@@ -3587,22 +3590,16 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>15</v>
-      </c>
-      <c r="C216" t="s">
-        <v>275</v>
-      </c>
-      <c r="D216">
-        <v>51</v>
+        <v>238</v>
       </c>
       <c r="E216" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="E217" t="str">
         <f t="shared" si="3"/>
@@ -3611,7 +3608,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="E218" t="str">
         <f t="shared" si="3"/>
@@ -3620,7 +3617,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>91</v>
+        <v>227</v>
       </c>
       <c r="E219" t="str">
         <f t="shared" si="3"/>
@@ -3629,7 +3626,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E220" t="str">
         <f t="shared" si="3"/>
@@ -3638,7 +3635,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E221" t="str">
         <f t="shared" si="3"/>
@@ -3647,7 +3644,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="E222" t="str">
         <f t="shared" si="3"/>
@@ -3656,7 +3653,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="E223" t="str">
         <f t="shared" si="3"/>
@@ -3665,7 +3662,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E224" t="str">
         <f t="shared" si="3"/>
@@ -3674,7 +3671,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="E225" t="str">
         <f t="shared" si="3"/>
@@ -3683,7 +3680,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="E226" t="str">
         <f t="shared" si="3"/>
@@ -3692,25 +3689,25 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="E227" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E227:E265" si="4">CONCATENATE("+",D227," ",B227)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E228" t="str">
-        <f t="shared" ref="E228:E266" si="4">CONCATENATE("+",D228," ",B228)</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="E229" t="str">
         <f t="shared" si="4"/>
@@ -3719,7 +3716,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="E230" t="str">
         <f t="shared" si="4"/>
@@ -3728,7 +3725,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="E231" t="str">
         <f t="shared" si="4"/>
@@ -3737,7 +3734,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E232" t="str">
         <f t="shared" si="4"/>
@@ -3746,7 +3743,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="E233" t="str">
         <f t="shared" si="4"/>
@@ -3755,19 +3752,25 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>123</v>
+        <v>73</v>
+      </c>
+      <c r="C234" t="s">
+        <v>274</v>
+      </c>
+      <c r="D234">
+        <v>51</v>
       </c>
       <c r="E234" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C235" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D235">
         <v>51</v>
@@ -3779,22 +3782,16 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>85</v>
-      </c>
-      <c r="C236" t="s">
-        <v>275</v>
-      </c>
-      <c r="D236">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="E236" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>227</v>
+        <v>143</v>
       </c>
       <c r="E237" t="str">
         <f t="shared" si="4"/>
@@ -3803,7 +3800,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>143</v>
+        <v>220</v>
       </c>
       <c r="E238" t="str">
         <f t="shared" si="4"/>
@@ -3812,19 +3809,25 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>221</v>
+        <v>258</v>
+      </c>
+      <c r="C239" t="s">
+        <v>274</v>
+      </c>
+      <c r="D239">
+        <v>51</v>
       </c>
       <c r="E239" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="C240" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D240">
         <v>51</v>
@@ -3836,10 +3839,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="C241" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D241">
         <v>51</v>
@@ -3851,40 +3854,34 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="B242">
+        <v>972691544</v>
       </c>
       <c r="C242" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D242">
         <v>51</v>
       </c>
       <c r="E242" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 972691544</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>13</v>
-      </c>
-      <c r="B243">
-        <v>972691544</v>
-      </c>
-      <c r="C243" t="s">
-        <v>275</v>
-      </c>
-      <c r="D243">
-        <v>51</v>
+        <v>187</v>
       </c>
       <c r="E243" t="str">
         <f t="shared" si="4"/>
-        <v>+51 972691544</v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E244" t="str">
         <f t="shared" si="4"/>
@@ -3893,7 +3890,7 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E245" t="str">
         <f t="shared" si="4"/>
@@ -3902,43 +3899,49 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>214</v>
+        <v>131</v>
+      </c>
+      <c r="C246" t="s">
+        <v>274</v>
+      </c>
+      <c r="D246">
+        <v>51</v>
       </c>
       <c r="E246" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>131</v>
-      </c>
-      <c r="C247" t="s">
-        <v>275</v>
-      </c>
-      <c r="D247">
-        <v>51</v>
+        <v>232</v>
       </c>
       <c r="E247" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>233</v>
+        <v>76</v>
+      </c>
+      <c r="C248" t="s">
+        <v>274</v>
+      </c>
+      <c r="D248">
+        <v>51</v>
       </c>
       <c r="E248" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C249" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D249">
         <v>51</v>
@@ -3950,34 +3953,34 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>49</v>
-      </c>
-      <c r="C250" t="s">
-        <v>275</v>
-      </c>
-      <c r="D250">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E250" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>24</v>
+        <v>102</v>
+      </c>
+      <c r="C251" t="s">
+        <v>274</v>
+      </c>
+      <c r="D251">
+        <v>51</v>
       </c>
       <c r="E251" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="C252" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D252">
         <v>51</v>
@@ -3989,22 +3992,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>171</v>
-      </c>
-      <c r="C253" t="s">
-        <v>275</v>
-      </c>
-      <c r="D253">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="E253" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="E254" t="str">
         <f t="shared" si="4"/>
@@ -4013,7 +4010,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="E255" t="str">
         <f t="shared" si="4"/>
@@ -4022,7 +4019,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="E256" t="str">
         <f t="shared" si="4"/>
@@ -4031,7 +4028,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>210</v>
+        <v>63</v>
       </c>
       <c r="E257" t="str">
         <f t="shared" si="4"/>
@@ -4040,7 +4037,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>63</v>
+        <v>228</v>
       </c>
       <c r="E258" t="str">
         <f t="shared" si="4"/>
@@ -4049,7 +4046,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E259" t="str">
         <f t="shared" si="4"/>
@@ -4058,7 +4055,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="E260" t="str">
         <f t="shared" si="4"/>
@@ -4067,7 +4064,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="E261" t="str">
         <f t="shared" si="4"/>
@@ -4076,7 +4073,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="E262" t="str">
         <f t="shared" si="4"/>
@@ -4085,7 +4082,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="E263" t="str">
         <f t="shared" si="4"/>
@@ -4094,7 +4091,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="E264" t="str">
         <f t="shared" si="4"/>
@@ -4103,40 +4100,31 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E265" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>11</v>
-      </c>
-      <c r="E266" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
+    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
-      <c r="E276" s="1"/>
-      <c r="F276" s="1"/>
-    </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B277" s="2"/>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
-      <c r="F277" s="2"/>
+      <c r="B276" s="2"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
+      <c r="F276" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A266" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A266">
-    <sortCondition ref="A2:A266"/>
+  <autoFilter ref="A1:A265" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A265">
+    <sortCondition ref="A2:A265"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33031367-9B3B-425A-AB6E-4E0019D147F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6840A94E-363C-4286-8512-333E7C90F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$A$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$273</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="382">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -774,9 +774,6 @@
     <t>Gcerbat</t>
   </si>
   <si>
-    <t>Mounstronio</t>
-  </si>
-  <si>
     <t>Lolo</t>
   </si>
   <si>
@@ -786,9 +783,6 @@
     <t>HideOnCube</t>
   </si>
   <si>
-    <t>ItsyaBoiGuz</t>
-  </si>
-  <si>
     <t>jztrkr</t>
   </si>
   <si>
@@ -822,9 +816,6 @@
     <t>Jupiter</t>
   </si>
   <si>
-    <t>Eduking</t>
-  </si>
-  <si>
     <t>Pendiente</t>
   </si>
   <si>
@@ -886,13 +877,319 @@
   </si>
   <si>
     <t>EEUU</t>
+  </si>
+  <si>
+    <t>933 668 277</t>
+  </si>
+  <si>
+    <t>980 596 555</t>
+  </si>
+  <si>
+    <t>424-7086947</t>
+  </si>
+  <si>
+    <t>412-1322018</t>
+  </si>
+  <si>
+    <t>985 699 608</t>
+  </si>
+  <si>
+    <t>1 56 1007 9583</t>
+  </si>
+  <si>
+    <t>1 81 2944 2313</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 984 190 584</t>
+  </si>
+  <si>
+    <t>984 267 160</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 912 858 811</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 646 20 50 99</t>
+  </si>
+  <si>
+    <t>416-4398466</t>
+  </si>
+  <si>
+    <t>322 4761144</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>949 647 819</t>
+  </si>
+  <si>
+    <t>950 746 501</t>
+  </si>
+  <si>
+    <t>71 9370-7438</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>412-7060529</t>
+  </si>
+  <si>
+    <t>601 36 84 69</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 917 057 695</t>
+  </si>
+  <si>
+    <t>608 39 51 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 912 209 142</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 920 449 371</t>
+  </si>
+  <si>
+    <t>8799 9543</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>1 686 589 5829</t>
+  </si>
+  <si>
+    <t>992 067 030</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 412-7396859</t>
+  </si>
+  <si>
+    <t>1 921 208 0809</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8936 2350</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>(253) 212-8032</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 912 058 374</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 96 083 0485</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>98 174 5020</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 983 379 394</t>
+  </si>
+  <si>
+    <t>980 679 898</t>
+  </si>
+  <si>
+    <t>9 3412 81-3587</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 302 5578252</t>
+  </si>
+  <si>
+    <t>96 151 5565</t>
+  </si>
+  <si>
+    <t>(809) 658-5500</t>
+  </si>
+  <si>
+    <t>424-1216695</t>
+  </si>
+  <si>
+    <t>963 745 855</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 983 752 2450</t>
+  </si>
+  <si>
+    <t>424-6956750</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 965 337 810</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 673 472 3074</t>
+  </si>
+  <si>
+    <t>1 55 1805 8456</t>
+  </si>
+  <si>
+    <t>98 768 2900</t>
+  </si>
+  <si>
+    <t>414-4473628</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 906 691 465</t>
+  </si>
+  <si>
+    <t>996 668 615</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 921 447 908</t>
+  </si>
+  <si>
+    <t>1 81 2684 3183</t>
+  </si>
+  <si>
+    <t>302 3773516</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9 11 2372-2211</t>
+  </si>
+  <si>
+    <t>960 749 072</t>
+  </si>
+  <si>
+    <t>984 784 816</t>
+  </si>
+  <si>
+    <t>970 857 085</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 945 349 568</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9 11 6135-9811</t>
+  </si>
+  <si>
+    <t>991 342 085</t>
+  </si>
+  <si>
+    <t>977 404 957</t>
+  </si>
+  <si>
+    <t>1 229 229 9515</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>986 824 543</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7139 5493</t>
+  </si>
+  <si>
+    <t>955 121 011</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 55 7364 9786</t>
+  </si>
+  <si>
+    <t>1 231 176 9718</t>
+  </si>
+  <si>
+    <t>981 000 049</t>
+  </si>
+  <si>
+    <t>9 7878 6558</t>
+  </si>
+  <si>
+    <t>973 614 848</t>
+  </si>
+  <si>
+    <t>971 942 638</t>
+  </si>
+  <si>
+    <t>422-0376517</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 834 252 9665</t>
+  </si>
+  <si>
+    <t>6082 6653</t>
+  </si>
+  <si>
+    <t>Republica Dominicana</t>
+  </si>
+  <si>
+    <t>4760 5947</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>763-2529</t>
+  </si>
+  <si>
+    <t>412-5885303</t>
+  </si>
+  <si>
+    <t>414-7234994</t>
+  </si>
+  <si>
+    <t>1 (849)</t>
+  </si>
+  <si>
+    <t>987 200 136</t>
+  </si>
+  <si>
+    <t>923 404 224</t>
+  </si>
+  <si>
+    <t>955 963 610</t>
+  </si>
+  <si>
+    <t>945 323 097</t>
+  </si>
+  <si>
+    <t>965 373 102</t>
+  </si>
+  <si>
+    <t>955 834 817</t>
+  </si>
+  <si>
+    <t>9 3794 12-0368</t>
+  </si>
+  <si>
+    <t>976 413 331</t>
+  </si>
+  <si>
+    <t>9 2974 22-6785</t>
+  </si>
+  <si>
+    <t>1 735 162 2046</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 756 103 6825</t>
+  </si>
+  <si>
+    <t>9 7927 3083</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 222 102 8165</t>
+  </si>
+  <si>
+    <t>3204-1711</t>
+  </si>
+  <si>
+    <t>Honduras</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,6 +1199,19 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -929,7 +1239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -937,6 +1247,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1251,7 +1563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1260,19 +1572,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E1" t="s">
         <v>264</v>
-      </c>
-      <c r="B1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1280,13 +1592,13 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D2">
         <v>51</v>
       </c>
       <c r="E2" t="str">
-        <f t="shared" ref="E2:E64" si="0">CONCATENATE("+",D2," ",B2)</f>
+        <f t="shared" ref="E2:E65" si="0">CONCATENATE("+",D2," ",B2)</f>
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
@@ -1294,42 +1606,54 @@
       <c r="A3" t="s">
         <v>237</v>
       </c>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D3">
         <v>51</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 933 668 277</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D4">
         <v>51</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 980 596 555</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
+      <c r="B5" t="s">
+        <v>282</v>
+      </c>
       <c r="C5" t="s">
-        <v>273</v>
+        <v>270</v>
+      </c>
+      <c r="D5">
+        <v>58</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58 424-7086947</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1337,7 +1661,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D6">
         <v>51</v>
@@ -1351,21 +1675,33 @@
       <c r="A7" t="s">
         <v>236</v>
       </c>
+      <c r="B7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7">
+        <v>58</v>
+      </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58 412-1322018</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>194</v>
       </c>
+      <c r="B8" t="s">
+        <v>378</v>
+      </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+ 9 7927 3083</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1373,7 +1709,7 @@
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -1383,49 +1719,58 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
+      <c r="B10" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="C10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D10">
         <v>51</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 985 699 608</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
+      <c r="B11" t="s">
+        <v>285</v>
+      </c>
       <c r="C11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D11">
         <v>52</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+52 </v>
+        <v>+52 1 56 1007 9583</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>192</v>
       </c>
+      <c r="B12" t="s">
+        <v>286</v>
+      </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D12">
         <v>52</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+52 </v>
+        <v>+52 1 81 2944 2313</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1433,7 +1778,7 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D13">
         <v>51</v>
@@ -1448,7 +1793,7 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D14">
         <v>51</v>
@@ -1463,7 +1808,7 @@
         <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D15">
         <v>51</v>
@@ -1477,21 +1822,27 @@
       <c r="A16" t="s">
         <v>22</v>
       </c>
+      <c r="B16" t="s">
+        <v>287</v>
+      </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D16">
         <v>51</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51  984 190 584</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
+      <c r="C17" t="s">
+        <v>294</v>
+      </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">+ </v>
@@ -1501,30 +1852,36 @@
       <c r="A18" t="s">
         <v>23</v>
       </c>
+      <c r="B18" t="s">
+        <v>288</v>
+      </c>
       <c r="C18" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D18">
         <v>51</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 984 267 160</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
+      <c r="B19" t="s">
+        <v>289</v>
+      </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D19">
         <v>51</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51  912 858 811</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1532,7 +1889,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -1543,18 +1900,36 @@
       <c r="A21" t="s">
         <v>136</v>
       </c>
+      <c r="B21" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D21">
+        <v>51</v>
+      </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 949 647 819</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
+      <c r="B22" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" t="s">
+        <v>290</v>
+      </c>
+      <c r="D22">
+        <v>34</v>
+      </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+34  646 20 50 99</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1570,18 +1945,36 @@
       <c r="A24" t="s">
         <v>137</v>
       </c>
+      <c r="B24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C24" t="s">
+        <v>268</v>
+      </c>
+      <c r="D24">
+        <v>52</v>
+      </c>
       <c r="E24" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52  1 222 102 8165</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
+      <c r="B25" t="s">
+        <v>292</v>
+      </c>
+      <c r="C25" t="s">
+        <v>270</v>
+      </c>
+      <c r="D25">
+        <v>58</v>
+      </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58 416-4398466</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1597,27 +1990,51 @@
       <c r="A27" t="s">
         <v>138</v>
       </c>
+      <c r="B27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27">
+        <v>57</v>
+      </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+57 322 4761144</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
+      <c r="C28" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28">
+        <v>52</v>
+      </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+52 </v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>235</v>
       </c>
+      <c r="B29" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" t="s">
+        <v>270</v>
+      </c>
+      <c r="D29">
+        <v>58</v>
+      </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58 412-7060529</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1628,7 +2045,7 @@
         <v>933448842</v>
       </c>
       <c r="C30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D30">
         <v>51</v>
@@ -1643,7 +2060,7 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -1666,9 +2083,18 @@
       <c r="A33" t="s">
         <v>180</v>
       </c>
+      <c r="B33" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" t="s">
+        <v>271</v>
+      </c>
+      <c r="D33">
+        <v>51</v>
+      </c>
       <c r="E33" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 950 746 501</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1676,10 +2102,10 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C34" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D34">
         <v>54</v>
@@ -1702,17 +2128,26 @@
       <c r="A36" t="s">
         <v>181</v>
       </c>
+      <c r="B36" t="s">
+        <v>297</v>
+      </c>
+      <c r="C36" t="s">
+        <v>298</v>
+      </c>
+      <c r="D36">
+        <v>55</v>
+      </c>
       <c r="E36" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+55 71 9370-7438</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D37">
         <v>51</v>
@@ -1726,9 +2161,18 @@
       <c r="A38" t="s">
         <v>121</v>
       </c>
+      <c r="B38" t="s">
+        <v>300</v>
+      </c>
+      <c r="C38" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38">
+        <v>34</v>
+      </c>
       <c r="E38" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+34 601 36 84 69</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1736,7 +2180,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D39">
         <v>51</v>
@@ -1750,24 +2194,36 @@
       <c r="A40" t="s">
         <v>185</v>
       </c>
+      <c r="B40" t="s">
+        <v>301</v>
+      </c>
       <c r="C40" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D40">
         <v>51</v>
       </c>
       <c r="E40" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51  917 057 695</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
+      <c r="B41" t="s">
+        <v>302</v>
+      </c>
+      <c r="C41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D41">
+        <v>34</v>
+      </c>
       <c r="E41" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+34 608 39 51 22</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,7 +2231,7 @@
         <v>222</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D42">
         <v>51</v>
@@ -1790,7 +2246,7 @@
         <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -1805,7 +2261,7 @@
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D44">
         <v>51</v>
@@ -1855,24 +2311,36 @@
       <c r="A49" t="s">
         <v>10</v>
       </c>
+      <c r="B49" t="s">
+        <v>304</v>
+      </c>
       <c r="C49" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D49">
         <v>51</v>
       </c>
       <c r="E49" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51  920 449 371</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
+      <c r="B50" t="s">
+        <v>303</v>
+      </c>
+      <c r="C50" t="s">
+        <v>271</v>
+      </c>
+      <c r="D50">
+        <v>51</v>
+      </c>
       <c r="E50" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51  912 209 142</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1888,42 +2356,69 @@
       <c r="A52" t="s">
         <v>0</v>
       </c>
+      <c r="B52" t="s">
+        <v>305</v>
+      </c>
+      <c r="C52" t="s">
+        <v>306</v>
+      </c>
+      <c r="D52">
+        <v>505</v>
+      </c>
       <c r="E52" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+505 8799 9543</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
+      <c r="B53" t="s">
+        <v>307</v>
+      </c>
+      <c r="C53" t="s">
+        <v>268</v>
+      </c>
+      <c r="D53">
+        <v>52</v>
+      </c>
       <c r="E53" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52 1 686 589 5829</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
+      <c r="B54" t="s">
+        <v>308</v>
+      </c>
       <c r="C54" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D54">
         <v>51</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 992 067 030</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
+      <c r="C55" t="s">
+        <v>294</v>
+      </c>
+      <c r="D55">
+        <v>57</v>
+      </c>
       <c r="E55" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+57 </v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1931,7 +2426,7 @@
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D56">
         <v>51</v>
@@ -1954,36 +2449,69 @@
       <c r="A58" t="s">
         <v>32</v>
       </c>
+      <c r="B58" t="s">
+        <v>309</v>
+      </c>
+      <c r="C58" t="s">
+        <v>270</v>
+      </c>
+      <c r="D58">
+        <v>58</v>
+      </c>
       <c r="E58" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58  412-7396859</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
+      <c r="B59" t="s">
+        <v>310</v>
+      </c>
+      <c r="C59" t="s">
+        <v>268</v>
+      </c>
+      <c r="D59">
+        <v>52</v>
+      </c>
       <c r="E59" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52 1 921 208 0809</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
+      <c r="C60" t="s">
+        <v>271</v>
+      </c>
+      <c r="D60">
+        <v>51</v>
+      </c>
       <c r="E60" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
+      <c r="B61" t="s">
+        <v>380</v>
+      </c>
+      <c r="C61" t="s">
+        <v>381</v>
+      </c>
+      <c r="D61">
+        <v>504</v>
+      </c>
       <c r="E61" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v>+504 3204-1711</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,9 +2527,15 @@
       <c r="A63" t="s">
         <v>223</v>
       </c>
+      <c r="C63" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63">
+        <v>51</v>
+      </c>
       <c r="E63" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2009,10 +2543,10 @@
         <v>39</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2027,7 +2561,7 @@
         <v>168</v>
       </c>
       <c r="E65" t="str">
-        <f t="shared" ref="E65:E99" si="1">CONCATENATE("+",D65," ",B65)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
@@ -2036,7 +2570,7 @@
         <v>124</v>
       </c>
       <c r="E66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E66:E127" si="1">CONCATENATE("+",D66," ",B66)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
@@ -2062,18 +2596,36 @@
       <c r="A69" t="s">
         <v>5</v>
       </c>
+      <c r="B69" t="s">
+        <v>311</v>
+      </c>
+      <c r="C69" t="s">
+        <v>312</v>
+      </c>
+      <c r="D69">
+        <v>506</v>
+      </c>
       <c r="E69" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+506  8936 2350</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
+      <c r="B70" t="s">
+        <v>313</v>
+      </c>
+      <c r="C70" t="s">
+        <v>279</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
       <c r="E70" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+1 (253) 212-8032</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2081,7 +2633,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D71">
         <v>51</v>
@@ -2093,7 +2645,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" si="1"/>
@@ -2102,7 +2654,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="1"/>
@@ -2111,7 +2663,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="1"/>
@@ -2120,28 +2672,43 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>188</v>
+        <v>241</v>
+      </c>
+      <c r="C75" t="s">
+        <v>273</v>
+      </c>
+      <c r="D75">
+        <v>54</v>
       </c>
       <c r="E75" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>241</v>
+        <v>31</v>
+      </c>
+      <c r="B76" t="s">
+        <v>314</v>
+      </c>
+      <c r="C76" t="s">
+        <v>271</v>
+      </c>
+      <c r="D76">
+        <v>51</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51  912 058 374</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D77">
         <v>51</v>
@@ -2153,22 +2720,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>88</v>
-      </c>
-      <c r="C78" t="s">
-        <v>274</v>
-      </c>
-      <c r="D78">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="E78" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E79" t="str">
         <f t="shared" si="1"/>
@@ -2177,7 +2738,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E80" t="str">
         <f t="shared" si="1"/>
@@ -2186,16 +2747,25 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>106</v>
+        <v>215</v>
+      </c>
+      <c r="B81" t="s">
+        <v>315</v>
+      </c>
+      <c r="C81" t="s">
+        <v>316</v>
+      </c>
+      <c r="D81">
+        <v>593</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+593  96 083 0485</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="E82" t="str">
         <f t="shared" si="1"/>
@@ -2204,7 +2774,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E83" t="str">
         <f t="shared" si="1"/>
@@ -2213,55 +2783,67 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>107</v>
+        <v>44</v>
+      </c>
+      <c r="B84" t="s">
+        <v>318</v>
+      </c>
+      <c r="C84" t="s">
+        <v>271</v>
+      </c>
+      <c r="D84">
+        <v>51</v>
       </c>
       <c r="E84" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51  983 379 394</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>44</v>
-      </c>
-      <c r="C85" t="s">
-        <v>274</v>
-      </c>
-      <c r="D85">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>66</v>
+        <v>162</v>
+      </c>
+      <c r="B86" t="s">
+        <v>319</v>
+      </c>
+      <c r="C86" t="s">
+        <v>271</v>
+      </c>
+      <c r="D86">
+        <v>51</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 980 679 898</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D87">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="E88" t="str">
         <f t="shared" si="1"/>
@@ -2270,7 +2852,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="E89" t="str">
         <f t="shared" si="1"/>
@@ -2279,16 +2861,22 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>176</v>
+        <v>122</v>
+      </c>
+      <c r="C90" t="s">
+        <v>316</v>
+      </c>
+      <c r="D90">
+        <v>593</v>
       </c>
       <c r="E90" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+593 </v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="E91" t="str">
         <f t="shared" si="1"/>
@@ -2297,43 +2885,76 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>214</v>
+        <v>45</v>
+      </c>
+      <c r="B92" t="s">
+        <v>320</v>
+      </c>
+      <c r="C92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92">
+        <v>54</v>
       </c>
       <c r="E92" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+54 9 3412 81-3587</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>45</v>
+        <v>89</v>
+      </c>
+      <c r="C93" t="s">
+        <v>271</v>
+      </c>
+      <c r="D93">
+        <v>51</v>
       </c>
       <c r="E93" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>89</v>
+        <v>120</v>
+      </c>
+      <c r="B94" t="s">
+        <v>321</v>
+      </c>
+      <c r="C94" t="s">
+        <v>294</v>
+      </c>
+      <c r="D94">
+        <v>57</v>
       </c>
       <c r="E94" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+57  302 5578252</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>206</v>
+      </c>
+      <c r="B95" t="s">
+        <v>322</v>
+      </c>
+      <c r="C95" t="s">
+        <v>316</v>
+      </c>
+      <c r="D95">
+        <v>593</v>
       </c>
       <c r="E95" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+593 96 151 5565</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="1"/>
@@ -2342,340 +2963,460 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>240</v>
+      </c>
+      <c r="B97" t="s">
+        <v>275</v>
+      </c>
+      <c r="C97" t="s">
+        <v>273</v>
+      </c>
+      <c r="D97">
+        <v>54</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+54 9 11 2783 9968</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>240</v>
-      </c>
-      <c r="B98" t="s">
-        <v>278</v>
-      </c>
-      <c r="C98" t="s">
-        <v>276</v>
-      </c>
-      <c r="D98">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="E98" t="str">
         <f t="shared" si="1"/>
-        <v>+54 9 11 2783 9968</v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>155</v>
+        <v>34</v>
+      </c>
+      <c r="B99" t="s">
+        <v>267</v>
+      </c>
+      <c r="C99" t="s">
+        <v>266</v>
+      </c>
+      <c r="D99">
+        <v>53</v>
       </c>
       <c r="E99" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+53 5 1113536</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>34</v>
-      </c>
-      <c r="B100" t="s">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="C100" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D100">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E100" t="str">
-        <f>CONCATENATE("+",D100," ",B100)</f>
-        <v>+53 5 1113536</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>140</v>
+        <v>233</v>
+      </c>
+      <c r="C101" t="s">
+        <v>273</v>
+      </c>
+      <c r="D101">
+        <v>54</v>
       </c>
       <c r="E101" t="str">
-        <f t="shared" ref="E101:E163" si="2">CONCATENATE("+",D101," ",B101)</f>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>233</v>
+        <v>141</v>
+      </c>
+      <c r="C102" t="s">
+        <v>294</v>
+      </c>
+      <c r="D102">
+        <v>57</v>
       </c>
       <c r="E102" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+57 </v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>141</v>
+        <v>55</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C103" t="s">
+        <v>279</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
       </c>
       <c r="E103" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+1 (809) 658-5500</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>55</v>
+        <v>154</v>
+      </c>
+      <c r="B104" t="s">
+        <v>324</v>
+      </c>
+      <c r="C104" t="s">
+        <v>270</v>
+      </c>
+      <c r="D104">
+        <v>58</v>
       </c>
       <c r="E104" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+58 424-1216695</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>169</v>
+      </c>
+      <c r="B105" t="s">
+        <v>325</v>
+      </c>
+      <c r="C105" t="s">
+        <v>271</v>
+      </c>
+      <c r="D105">
+        <v>51</v>
       </c>
       <c r="E105" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+51 963 745 855</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>169</v>
-      </c>
-      <c r="C106" t="s">
-        <v>274</v>
-      </c>
-      <c r="D106">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="E106" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>225</v>
+        <v>114</v>
+      </c>
+      <c r="B107" t="s">
+        <v>331</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
       </c>
       <c r="E107" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+ 98 768 2900</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E108" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="E109" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>248</v>
+        <v>243</v>
+      </c>
+      <c r="C110" t="s">
+        <v>271</v>
+      </c>
+      <c r="D110">
+        <v>51</v>
       </c>
       <c r="E110" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>243</v>
+        <v>156</v>
+      </c>
+      <c r="B111" t="s">
+        <v>332</v>
+      </c>
+      <c r="C111" t="s">
+        <v>270</v>
+      </c>
+      <c r="D111">
+        <v>58</v>
       </c>
       <c r="E111" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+58 414-4473628</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="E112" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>43</v>
+        <v>224</v>
+      </c>
+      <c r="C113" t="s">
+        <v>271</v>
+      </c>
+      <c r="D113">
+        <v>51</v>
       </c>
       <c r="E113" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>249</v>
+        <v>163</v>
+      </c>
+      <c r="C114" t="s">
+        <v>271</v>
+      </c>
+      <c r="D114">
+        <v>51</v>
       </c>
       <c r="E114" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>224</v>
+        <v>56</v>
       </c>
       <c r="E115" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="E116" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>56</v>
+        <v>130</v>
+      </c>
+      <c r="B117" t="s">
+        <v>333</v>
+      </c>
+      <c r="C117" t="s">
+        <v>271</v>
+      </c>
+      <c r="D117">
+        <v>51</v>
       </c>
       <c r="E117" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+51  906 691 465</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>150</v>
+        <v>146</v>
+      </c>
+      <c r="C118" t="s">
+        <v>271</v>
+      </c>
+      <c r="D118">
+        <v>51</v>
       </c>
       <c r="E118" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="E119" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="E120" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="E121" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>46</v>
+        <v>2</v>
+      </c>
+      <c r="C122" t="s">
+        <v>271</v>
+      </c>
+      <c r="D122">
+        <v>51</v>
       </c>
       <c r="E122" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>210</v>
+        <v>21</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C123" t="s">
+        <v>271</v>
+      </c>
+      <c r="D123">
+        <v>51</v>
       </c>
       <c r="E123" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v>+51 996 668 615</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="C124" t="s">
+        <v>271</v>
+      </c>
+      <c r="D124">
+        <v>51</v>
       </c>
       <c r="E124" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>21</v>
-      </c>
-      <c r="C125" t="s">
-        <v>274</v>
-      </c>
-      <c r="D125">
-        <v>51</v>
+        <v>250</v>
       </c>
       <c r="E125" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>77</v>
-      </c>
-      <c r="C126" t="s">
-        <v>274</v>
-      </c>
-      <c r="D126">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="E126" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>252</v>
+        <v>254</v>
+      </c>
+      <c r="B127" t="s">
+        <v>335</v>
+      </c>
+      <c r="C127" t="s">
+        <v>271</v>
+      </c>
+      <c r="D127">
+        <v>51</v>
       </c>
       <c r="E127" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>+51  921 447 908</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C128" t="s">
+        <v>271</v>
+      </c>
+      <c r="D128">
+        <v>51</v>
       </c>
       <c r="E128" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" ref="E128:E190" si="2">CONCATENATE("+",D128," ",B128)</f>
+        <v>+51 976 413 331</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>256</v>
+        <v>184</v>
+      </c>
+      <c r="C129" t="s">
+        <v>271</v>
+      </c>
+      <c r="D129">
+        <v>51</v>
       </c>
       <c r="E129" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="E130" t="str">
         <f t="shared" si="2"/>
@@ -2684,25 +3425,37 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>184</v>
+        <v>157</v>
+      </c>
+      <c r="C131" t="s">
+        <v>273</v>
+      </c>
+      <c r="D131">
+        <v>54</v>
       </c>
       <c r="E131" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>101</v>
+        <v>47</v>
+      </c>
+      <c r="C132" t="s">
+        <v>294</v>
+      </c>
+      <c r="D132">
+        <v>57</v>
       </c>
       <c r="E132" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+57 </v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="E133" t="str">
         <f t="shared" si="2"/>
@@ -2711,16 +3464,25 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>47</v>
+        <v>258</v>
+      </c>
+      <c r="B134" t="s">
+        <v>276</v>
+      </c>
+      <c r="C134" t="s">
+        <v>273</v>
+      </c>
+      <c r="D134">
+        <v>54</v>
       </c>
       <c r="E134" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+54 9 11 2526 8333</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="E135" t="str">
         <f t="shared" si="2"/>
@@ -2729,25 +3491,25 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>260</v>
+        <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="C136" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D136">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E136" t="str">
         <f t="shared" si="2"/>
-        <v>+54 9 11 2526 8333</v>
+        <v>+52 1 81 2684 3183</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="E137" t="str">
         <f t="shared" si="2"/>
@@ -2756,100 +3518,142 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>33</v>
+        <v>179</v>
       </c>
       <c r="C138" t="s">
         <v>271</v>
       </c>
       <c r="D138">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E138" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+52 </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>109</v>
+      </c>
+      <c r="C139" t="s">
+        <v>271</v>
+      </c>
+      <c r="D139">
+        <v>51</v>
       </c>
       <c r="E139" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="E140" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>109</v>
+        <v>26</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C141" t="s">
+        <v>294</v>
+      </c>
+      <c r="D141">
+        <v>57</v>
       </c>
       <c r="E141" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+57 302 3773516</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>18</v>
+      </c>
+      <c r="B142" t="s">
+        <v>338</v>
+      </c>
+      <c r="C142" t="s">
+        <v>273</v>
+      </c>
+      <c r="D142">
+        <v>54</v>
       </c>
       <c r="E142" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+54  9 11 2372-2211</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>26</v>
+        <v>212</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C143" t="s">
+        <v>271</v>
+      </c>
+      <c r="D143">
+        <v>51</v>
       </c>
       <c r="E143" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 960 749 072</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>340</v>
+      </c>
+      <c r="C144" t="s">
+        <v>271</v>
+      </c>
+      <c r="D144">
+        <v>51</v>
       </c>
       <c r="E144" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 984 784 816</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>212</v>
+        <v>245</v>
+      </c>
+      <c r="C145" t="s">
+        <v>271</v>
+      </c>
+      <c r="D145">
+        <v>51</v>
       </c>
       <c r="E145" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>25</v>
-      </c>
-      <c r="C146" t="s">
-        <v>274</v>
-      </c>
-      <c r="D146">
-        <v>51</v>
+        <v>208</v>
       </c>
       <c r="E146" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="E147" t="str">
         <f t="shared" si="2"/>
@@ -2858,7 +3662,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="E148" t="str">
         <f t="shared" si="2"/>
@@ -2867,55 +3671,91 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>211</v>
+        <v>186</v>
+      </c>
+      <c r="C149" t="s">
+        <v>273</v>
+      </c>
+      <c r="D149">
+        <v>54</v>
       </c>
       <c r="E149" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>175</v>
+        <v>65</v>
+      </c>
+      <c r="B150" t="s">
+        <v>317</v>
+      </c>
+      <c r="C150" t="s">
+        <v>316</v>
+      </c>
+      <c r="D150" s="4">
+        <v>593</v>
       </c>
       <c r="E150" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+593 98 174 5020</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>186</v>
+        <v>4</v>
+      </c>
+      <c r="C151" t="s">
+        <v>271</v>
+      </c>
+      <c r="D151">
+        <v>51</v>
       </c>
       <c r="E151" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>65</v>
+        <v>118</v>
+      </c>
+      <c r="C152" t="s">
+        <v>271</v>
+      </c>
+      <c r="D152">
+        <v>51</v>
       </c>
       <c r="E152" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>4</v>
+        <v>173</v>
+      </c>
+      <c r="B153" t="s">
+        <v>269</v>
+      </c>
+      <c r="C153" t="s">
+        <v>268</v>
+      </c>
+      <c r="D153">
+        <v>52</v>
       </c>
       <c r="E153" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52 1 771 297 6010</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="C154" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D154">
         <v>51</v>
@@ -2927,70 +3767,94 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B155" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="C155" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D155">
         <v>52</v>
       </c>
       <c r="E155" t="str">
         <f t="shared" si="2"/>
-        <v>+52 1 771 297 6010</v>
+        <v>+52  1 983 752 2450</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>178</v>
+        <v>93</v>
+      </c>
+      <c r="C156" t="s">
+        <v>271</v>
+      </c>
+      <c r="D156">
+        <v>51</v>
       </c>
       <c r="E156" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>189</v>
+        <v>153</v>
+      </c>
+      <c r="B157" t="s">
+        <v>327</v>
+      </c>
+      <c r="C157" t="s">
+        <v>270</v>
+      </c>
+      <c r="D157">
+        <v>58</v>
       </c>
       <c r="E157" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58 424-6956750</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>93</v>
+        <v>72</v>
+      </c>
+      <c r="B158" t="s">
+        <v>328</v>
       </c>
       <c r="C158" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D158">
         <v>51</v>
       </c>
       <c r="E158" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51  965 337 810</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>153</v>
+        <v>86</v>
+      </c>
+      <c r="C159" t="s">
+        <v>271</v>
+      </c>
+      <c r="D159">
+        <v>51</v>
       </c>
       <c r="E159" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C160" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D160">
         <v>51</v>
@@ -3002,346 +3866,490 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>86</v>
+        <v>75</v>
+      </c>
+      <c r="C161" t="s">
+        <v>271</v>
+      </c>
+      <c r="D161">
+        <v>51</v>
       </c>
       <c r="E161" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="C162" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D162">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E162" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>75</v>
+        <v>253</v>
+      </c>
+      <c r="B163" t="s">
+        <v>342</v>
       </c>
       <c r="C163" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D163">
         <v>51</v>
       </c>
       <c r="E163" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51  945 349 568</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>201</v>
+        <v>252</v>
+      </c>
+      <c r="B164" t="s">
+        <v>376</v>
+      </c>
+      <c r="C164" t="s">
+        <v>268</v>
+      </c>
+      <c r="D164">
+        <v>52</v>
       </c>
       <c r="E164" t="str">
-        <f t="shared" ref="E164:E226" si="3">CONCATENATE("+",D164," ",B164)</f>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>+52 1 735 162 2046</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>255</v>
+        <v>246</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C165" t="s">
+        <v>271</v>
+      </c>
+      <c r="D165">
+        <v>51</v>
       </c>
       <c r="E165" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+51 970 857 085</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>254</v>
+        <v>78</v>
+      </c>
+      <c r="C166" t="s">
+        <v>271</v>
+      </c>
+      <c r="D166">
+        <v>51</v>
       </c>
       <c r="E166" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>247</v>
+        <v>147</v>
+      </c>
+      <c r="B167" t="s">
+        <v>329</v>
       </c>
       <c r="C167" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D167">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E167" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="2"/>
+        <v>+52  1 673 472 3074</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>78</v>
+        <v>59</v>
+      </c>
+      <c r="B168" t="s">
+        <v>375</v>
       </c>
       <c r="C168" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D168">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E168" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="2"/>
+        <v>+54 9 2974 22-6785</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>147</v>
+        <v>242</v>
+      </c>
+      <c r="B169" t="s">
+        <v>330</v>
+      </c>
+      <c r="C169" t="s">
+        <v>268</v>
+      </c>
+      <c r="D169">
+        <v>52</v>
       </c>
       <c r="E169" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+52 1 55 1805 8456</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>59</v>
+        <v>234</v>
+      </c>
+      <c r="C170" t="s">
+        <v>268</v>
+      </c>
+      <c r="D170">
+        <v>52</v>
       </c>
       <c r="E170" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+52 </v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>242</v>
+        <v>35</v>
+      </c>
+      <c r="B171" t="s">
+        <v>343</v>
+      </c>
+      <c r="C171" t="s">
+        <v>273</v>
+      </c>
+      <c r="D171">
+        <v>54</v>
       </c>
       <c r="E171" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+54  9 11 6135-9811</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="E172" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+ </v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>245</v>
+        <v>219</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C173" t="s">
+        <v>271</v>
+      </c>
+      <c r="D173">
+        <v>51</v>
       </c>
       <c r="E173" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+51 991 342 085</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="C174" t="s">
+        <v>312</v>
+      </c>
+      <c r="D174">
+        <v>506</v>
       </c>
       <c r="E174" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+506 </v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>202</v>
+        <v>218</v>
+      </c>
+      <c r="C175" t="s">
+        <v>271</v>
+      </c>
+      <c r="D175">
+        <v>51</v>
       </c>
       <c r="E175" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="E176" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>69</v>
+        <v>257</v>
+      </c>
+      <c r="B177" t="s">
+        <v>277</v>
+      </c>
+      <c r="C177" t="s">
+        <v>266</v>
+      </c>
+      <c r="D177">
+        <v>53</v>
       </c>
       <c r="E177" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+53 5 6957902</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>218</v>
-      </c>
-      <c r="C178" t="s">
-        <v>274</v>
-      </c>
-      <c r="D178">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="E178" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="E179" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+ </v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>259</v>
-      </c>
-      <c r="B180" t="s">
-        <v>280</v>
+        <v>29</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="C180" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D180">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E180" t="str">
-        <f t="shared" si="3"/>
-        <v>+53 5 6957902</v>
+        <f t="shared" si="2"/>
+        <v>+51 977 404 957</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>134</v>
+        <v>53</v>
+      </c>
+      <c r="B181" t="s">
+        <v>346</v>
+      </c>
+      <c r="C181" t="s">
+        <v>268</v>
+      </c>
+      <c r="D181">
+        <v>52</v>
       </c>
       <c r="E181" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>+52 1 229 229 9515</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>132</v>
+        <v>64</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C182" t="s">
+        <v>271</v>
+      </c>
+      <c r="D182">
+        <v>51</v>
       </c>
       <c r="E182" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+51 986 824 543</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>29</v>
+        <v>16</v>
+      </c>
+      <c r="B183">
+        <v>69865757</v>
       </c>
       <c r="C183" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="D183">
-        <v>51</v>
+        <v>591</v>
       </c>
       <c r="E183" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="2"/>
+        <v>+591 69865757</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="B184" t="s">
+        <v>349</v>
+      </c>
+      <c r="C184" t="s">
+        <v>312</v>
+      </c>
+      <c r="D184">
+        <v>506</v>
       </c>
       <c r="E184" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+506  7139 5493</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>64</v>
+        <v>115</v>
+      </c>
+      <c r="C185" t="s">
+        <v>270</v>
+      </c>
+      <c r="D185">
+        <v>58</v>
       </c>
       <c r="E185" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+58 </v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>16</v>
+        <v>198</v>
+      </c>
+      <c r="C186" t="s">
+        <v>270</v>
+      </c>
+      <c r="D186">
+        <v>58</v>
       </c>
       <c r="E186" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+58 </v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>58</v>
+        <v>207</v>
       </c>
       <c r="E187" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>115</v>
+        <v>3</v>
+      </c>
+      <c r="B188" t="s">
+        <v>350</v>
+      </c>
+      <c r="C188" t="s">
+        <v>271</v>
+      </c>
+      <c r="D188">
+        <v>51</v>
       </c>
       <c r="E188" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v>+51 955 121 011</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>198</v>
+        <v>172</v>
+      </c>
+      <c r="C189" t="s">
+        <v>271</v>
+      </c>
+      <c r="D189">
+        <v>51</v>
       </c>
       <c r="E189" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="E190" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" t="s">
-        <v>274</v>
-      </c>
-      <c r="D191">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="E191" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" ref="E191:E254" si="3">CONCATENATE("+",D191," ",B191)</f>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>172</v>
+        <v>103</v>
+      </c>
+      <c r="C192" t="s">
+        <v>271</v>
+      </c>
+      <c r="D192">
+        <v>51</v>
       </c>
       <c r="E192" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>104</v>
+        <v>259</v>
       </c>
       <c r="E193" t="str">
         <f t="shared" si="3"/>
@@ -3350,31 +4358,40 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>152</v>
+        <v>80</v>
+      </c>
+      <c r="C194" t="s">
+        <v>271</v>
+      </c>
+      <c r="D194">
+        <v>51</v>
       </c>
       <c r="E194" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>103</v>
+        <v>190</v>
+      </c>
+      <c r="B195" t="s">
+        <v>377</v>
       </c>
       <c r="C195" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D195">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E195" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+52  1 756 103 6825</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="E196" t="str">
         <f t="shared" si="3"/>
@@ -3383,16 +4400,22 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>80</v>
+        <v>174</v>
+      </c>
+      <c r="C197" t="s">
+        <v>271</v>
+      </c>
+      <c r="D197">
+        <v>51</v>
       </c>
       <c r="E197" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E198" t="str">
         <f t="shared" si="3"/>
@@ -3401,40 +4424,52 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>204</v>
+        <v>48</v>
+      </c>
+      <c r="B199" t="s">
+        <v>352</v>
+      </c>
+      <c r="C199" t="s">
+        <v>268</v>
+      </c>
+      <c r="D199">
+        <v>52</v>
       </c>
       <c r="E199" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52 1 231 176 9718</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>174</v>
-      </c>
-      <c r="C200" t="s">
-        <v>274</v>
-      </c>
-      <c r="D200">
-        <v>51</v>
+        <v>249</v>
       </c>
       <c r="E200" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>351</v>
+      </c>
+      <c r="C201" t="s">
+        <v>268</v>
+      </c>
+      <c r="D201">
+        <v>52</v>
       </c>
       <c r="E201" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52  1 55 7364 9786</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="E202" t="str">
         <f t="shared" si="3"/>
@@ -3443,16 +4478,22 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>251</v>
+        <v>183</v>
+      </c>
+      <c r="C203" t="s">
+        <v>271</v>
+      </c>
+      <c r="D203">
+        <v>51</v>
       </c>
       <c r="E203" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E204" t="str">
         <f t="shared" si="3"/>
@@ -3461,7 +4502,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="E205" t="str">
         <f t="shared" si="3"/>
@@ -3470,115 +4511,154 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>183</v>
-      </c>
-      <c r="C206" t="s">
-        <v>274</v>
-      </c>
-      <c r="D206">
-        <v>51</v>
+        <v>251</v>
       </c>
       <c r="E206" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>196</v>
+        <v>97</v>
+      </c>
+      <c r="C207" t="s">
+        <v>271</v>
+      </c>
+      <c r="D207">
+        <v>51</v>
       </c>
       <c r="E207" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>96</v>
+        <v>28</v>
+      </c>
+      <c r="B208" t="s">
+        <v>353</v>
+      </c>
+      <c r="C208" t="s">
+        <v>271</v>
+      </c>
+      <c r="D208">
+        <v>51</v>
       </c>
       <c r="E208" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 981 000 049</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>253</v>
+        <v>191</v>
+      </c>
+      <c r="C209" t="s">
+        <v>271</v>
+      </c>
+      <c r="D209">
+        <v>51</v>
       </c>
       <c r="E209" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>97</v>
+        <v>145</v>
+      </c>
+      <c r="B210" t="s">
+        <v>354</v>
       </c>
       <c r="C210" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D210">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E210" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+56 9 7878 6558</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>28</v>
+        <v>7</v>
+      </c>
+      <c r="B211" t="s">
+        <v>355</v>
       </c>
       <c r="C211" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D211">
         <v>51</v>
       </c>
       <c r="E211" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 973 614 848</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>191</v>
+        <v>15</v>
+      </c>
+      <c r="B212" t="s">
+        <v>356</v>
+      </c>
+      <c r="C212" t="s">
+        <v>271</v>
+      </c>
+      <c r="D212">
+        <v>51</v>
       </c>
       <c r="E212" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 971 942 638</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>145</v>
+        <v>238</v>
+      </c>
+      <c r="C213" t="s">
+        <v>271</v>
+      </c>
+      <c r="D213">
+        <v>51</v>
       </c>
       <c r="E213" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="B214" t="s">
+        <v>357</v>
       </c>
       <c r="C214" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D214">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E214" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+58 422-0376517</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="C215" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D215">
         <v>51</v>
@@ -3590,25 +4670,43 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>238</v>
+        <v>227</v>
+      </c>
+      <c r="B216" t="s">
+        <v>358</v>
+      </c>
+      <c r="C216" t="s">
+        <v>268</v>
+      </c>
+      <c r="D216">
+        <v>52</v>
       </c>
       <c r="E216" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52  1 834 252 9665</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>40</v>
+        <v>14</v>
+      </c>
+      <c r="B217" t="s">
+        <v>359</v>
+      </c>
+      <c r="C217" t="s">
+        <v>312</v>
+      </c>
+      <c r="D217">
+        <v>506</v>
       </c>
       <c r="E217" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+506 6082 6653</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E218" t="str">
         <f t="shared" si="3"/>
@@ -3617,515 +4715,648 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>227</v>
+        <v>116</v>
+      </c>
+      <c r="C219" t="s">
+        <v>273</v>
+      </c>
+      <c r="D219">
+        <v>54</v>
       </c>
       <c r="E219" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>14</v>
+        <v>164</v>
+      </c>
+      <c r="C220" t="s">
+        <v>271</v>
+      </c>
+      <c r="D220">
+        <v>51</v>
       </c>
       <c r="E220" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>67</v>
+        <v>148</v>
+      </c>
+      <c r="B221" t="s">
+        <v>364</v>
+      </c>
+      <c r="C221" t="s">
+        <v>270</v>
+      </c>
+      <c r="D221">
+        <v>58</v>
       </c>
       <c r="E221" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+58 412-5885303</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>116</v>
+        <v>98</v>
+      </c>
+      <c r="C222" t="s">
+        <v>273</v>
+      </c>
+      <c r="D222">
+        <v>54</v>
       </c>
       <c r="E222" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>164</v>
+        <v>260</v>
+      </c>
+      <c r="C223" t="s">
+        <v>271</v>
+      </c>
+      <c r="D223">
+        <v>51</v>
       </c>
       <c r="E223" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>148</v>
+        <v>79</v>
+      </c>
+      <c r="C224" t="s">
+        <v>271</v>
+      </c>
+      <c r="D224">
+        <v>51</v>
       </c>
       <c r="E224" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>98</v>
+        <v>60</v>
+      </c>
+      <c r="B225" t="s">
+        <v>365</v>
+      </c>
+      <c r="C225" t="s">
+        <v>268</v>
+      </c>
+      <c r="D225">
+        <v>52</v>
       </c>
       <c r="E225" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52 414-7234994</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>263</v>
+        <v>158</v>
+      </c>
+      <c r="B226" t="s">
+        <v>363</v>
+      </c>
+      <c r="C226" t="s">
+        <v>360</v>
+      </c>
+      <c r="D226" t="s">
+        <v>366</v>
       </c>
       <c r="E226" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
+        <v>+1 (849) 763-2529</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="E227" t="str">
-        <f t="shared" ref="E227:E265" si="4">CONCATENATE("+",D227," ",B227)</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>60</v>
+        <v>6</v>
+      </c>
+      <c r="C228" t="s">
+        <v>271</v>
+      </c>
+      <c r="D228">
+        <v>51</v>
       </c>
       <c r="E228" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="E229" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>197</v>
+        <v>123</v>
+      </c>
+      <c r="C230" t="s">
+        <v>273</v>
+      </c>
+      <c r="D230">
+        <v>54</v>
       </c>
       <c r="E230" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>6</v>
+        <v>73</v>
+      </c>
+      <c r="C231" t="s">
+        <v>271</v>
+      </c>
+      <c r="D231">
+        <v>51</v>
       </c>
       <c r="E231" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>36</v>
+        <v>85</v>
+      </c>
+      <c r="C232" t="s">
+        <v>271</v>
+      </c>
+      <c r="D232">
+        <v>51</v>
       </c>
       <c r="E232" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>123</v>
+        <v>226</v>
+      </c>
+      <c r="C233" t="s">
+        <v>273</v>
+      </c>
+      <c r="D233">
+        <v>54</v>
       </c>
       <c r="E233" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="C234" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D234">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E234" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>85</v>
-      </c>
-      <c r="C235" t="s">
-        <v>274</v>
-      </c>
-      <c r="D235">
-        <v>51</v>
+        <v>220</v>
       </c>
       <c r="E235" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+ </v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>226</v>
+        <v>256</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C236" t="s">
+        <v>271</v>
+      </c>
+      <c r="D236">
+        <v>51</v>
       </c>
       <c r="E236" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v>+51 923 404 224</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>143</v>
+        <v>81</v>
+      </c>
+      <c r="C237" t="s">
+        <v>271</v>
+      </c>
+      <c r="D237">
+        <v>51</v>
       </c>
       <c r="E237" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>220</v>
+        <v>19</v>
+      </c>
+      <c r="B238" t="s">
+        <v>367</v>
+      </c>
+      <c r="C238" t="s">
+        <v>271</v>
+      </c>
+      <c r="D238">
+        <v>51</v>
       </c>
       <c r="E238" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v>+51 987 200 136</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>258</v>
+        <v>13</v>
+      </c>
+      <c r="B239">
+        <v>972691544</v>
       </c>
       <c r="C239" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D239">
         <v>51</v>
       </c>
       <c r="E239" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="3"/>
+        <v>+51 972691544</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>81</v>
-      </c>
-      <c r="C240" t="s">
-        <v>274</v>
-      </c>
-      <c r="D240">
-        <v>51</v>
+        <v>187</v>
       </c>
       <c r="E240" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>19</v>
-      </c>
-      <c r="C241" t="s">
-        <v>274</v>
-      </c>
-      <c r="D241">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="E241" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>13</v>
-      </c>
-      <c r="B242">
-        <v>972691544</v>
-      </c>
-      <c r="C242" t="s">
-        <v>274</v>
-      </c>
-      <c r="D242">
-        <v>51</v>
+        <v>213</v>
       </c>
       <c r="E242" t="str">
-        <f t="shared" si="4"/>
-        <v>+51 972691544</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>187</v>
+        <v>131</v>
+      </c>
+      <c r="C243" t="s">
+        <v>271</v>
+      </c>
+      <c r="D243">
+        <v>51</v>
       </c>
       <c r="E243" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>205</v>
+        <v>232</v>
+      </c>
+      <c r="C244" t="s">
+        <v>273</v>
+      </c>
+      <c r="D244">
+        <v>54</v>
       </c>
       <c r="E244" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+54 </v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>213</v>
+        <v>76</v>
+      </c>
+      <c r="C245" t="s">
+        <v>271</v>
+      </c>
+      <c r="D245">
+        <v>51</v>
       </c>
       <c r="E245" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="C246" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D246">
         <v>51</v>
       </c>
       <c r="E246" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>232</v>
+        <v>24</v>
       </c>
       <c r="E247" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="B248" t="s">
+        <v>369</v>
       </c>
       <c r="C248" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D248">
         <v>51</v>
       </c>
       <c r="E248" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="3"/>
+        <v>+51 955 963 610</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="C249" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D249">
         <v>51</v>
       </c>
       <c r="E249" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>24</v>
+        <v>182</v>
+      </c>
+      <c r="C250" t="s">
+        <v>271</v>
+      </c>
+      <c r="D250">
+        <v>51</v>
       </c>
       <c r="E250" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C251" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D251">
         <v>51</v>
       </c>
       <c r="E251" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="C252" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D252">
         <v>51</v>
       </c>
       <c r="E252" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+51 </v>
+        <f t="shared" si="3"/>
+        <v>+51 945 323 097</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="E253" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>82</v>
+        <v>63</v>
+      </c>
+      <c r="B254" t="s">
+        <v>371</v>
+      </c>
+      <c r="C254" t="s">
+        <v>271</v>
+      </c>
+      <c r="D254">
+        <v>51</v>
       </c>
       <c r="E254" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
+        <f t="shared" si="3"/>
+        <v>+51 965 373 102</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1</v>
+        <v>228</v>
       </c>
       <c r="E255" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E255:E262" si="4">CONCATENATE("+",D255," ",B255)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="E256" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>63</v>
+        <v>216</v>
+      </c>
+      <c r="C257" t="s">
+        <v>270</v>
+      </c>
+      <c r="D257">
+        <v>58</v>
       </c>
       <c r="E257" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>228</v>
+        <v>70</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C258" t="s">
+        <v>271</v>
+      </c>
+      <c r="D258">
+        <v>51</v>
       </c>
       <c r="E258" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+51 955 834 817</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>239</v>
+        <v>144</v>
       </c>
       <c r="E259" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>216</v>
+        <v>95</v>
       </c>
       <c r="E260" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="B261" t="s">
+        <v>373</v>
+      </c>
+      <c r="C261" t="s">
+        <v>273</v>
+      </c>
+      <c r="D261">
+        <v>54</v>
       </c>
       <c r="E261" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+54 9 3794 12-0368</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>144</v>
+        <v>11</v>
+      </c>
+      <c r="B262" t="s">
+        <v>361</v>
+      </c>
+      <c r="C262" t="s">
+        <v>362</v>
+      </c>
+      <c r="D262">
+        <v>502</v>
       </c>
       <c r="E262" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>95</v>
-      </c>
-      <c r="E263" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>62</v>
-      </c>
-      <c r="E264" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>11</v>
-      </c>
-      <c r="E265" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
-      <c r="E275" s="1"/>
-      <c r="F275" s="1"/>
-    </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B276" s="2"/>
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
+        <v>+502 4760 5947</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+    </row>
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A265" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A265">
-    <sortCondition ref="A2:A265"/>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
+    <sortCondition ref="A2:A262"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6840A94E-363C-4286-8512-333E7C90F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15588B52-122F-4FA8-B0B2-20B64A6E1F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15588B52-122F-4FA8-B0B2-20B64A6E1F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4389179F-C8E3-4303-8D0A-F307D58E4014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="383">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1183,6 +1183,9 @@
   </si>
   <si>
     <t>Honduras</t>
+  </si>
+  <si>
+    <t>1 444 674 9780</t>
   </si>
 </sst>
 </file>
@@ -3292,9 +3295,18 @@
       <c r="A121" t="s">
         <v>210</v>
       </c>
+      <c r="B121" t="s">
+        <v>382</v>
+      </c>
+      <c r="C121" t="s">
+        <v>268</v>
+      </c>
+      <c r="D121">
+        <v>52</v>
+      </c>
       <c r="E121" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
+        <v>+52 1 444 674 9780</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">

--- a/celulares_.xlsx
+++ b/celulares_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4389179F-C8E3-4303-8D0A-F307D58E4014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6D66B5-7C70-45B5-B3D2-DBEEA7FBF404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView minimized="1" xWindow="7650" yWindow="4635" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="387">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1186,13 +1186,25 @@
   </si>
   <si>
     <t>1 444 674 9780</t>
+  </si>
+  <si>
+    <t>412-8286364</t>
+  </si>
+  <si>
+    <t>JohanSalapo</t>
+  </si>
+  <si>
+    <t>Jaspersd25</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1221,6 +1233,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD8D8D8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1242,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1252,6 +1270,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5249,7 +5268,7 @@
         <v>228</v>
       </c>
       <c r="E255" t="str">
-        <f t="shared" ref="E255:E262" si="4">CONCATENATE("+",D255," ",B255)</f>
+        <f t="shared" ref="E255:E263" si="4">CONCATENATE("+",D255," ",B255)</f>
         <v xml:space="preserve">+ </v>
       </c>
     </row>
@@ -5347,6 +5366,32 @@
       <c r="E262" t="str">
         <f t="shared" si="4"/>
         <v>+502 4760 5947</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>384</v>
+      </c>
+      <c r="B263" t="s">
+        <v>383</v>
+      </c>
+      <c r="C263" t="s">
+        <v>270</v>
+      </c>
+      <c r="D263">
+        <v>58</v>
+      </c>
+      <c r="E263" t="str">
+        <f t="shared" si="4"/>
+        <v>+58 412-8286364</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C264" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
